--- a/nablarch_sample/アプリケーション方式設計書_6出力処理方式_6.3メール送信.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_6出力処理方式_6.3メール送信.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF41399-A5E0-48FD-BC34-DA2F02CD7B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B720D016-DA04-49C4-B6A2-91106C764AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.3.メール送信" sheetId="3" r:id="rId1"/>
@@ -814,10 +814,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/mail.html#mail-request</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>本処理方式では、本システムから出力するメール送信処理を対象とする。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -988,6 +984,10 @@
     <rPh sb="24" eb="26">
       <t>ヨウイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/mail.html#mail-request</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -998,7 +998,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1043,6 +1043,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -1427,9 +1436,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1495,6 +1501,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1834,146 +1843,146 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI508"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="3.625" style="4"/>
-    <col min="6" max="6" width="3.625" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="3.625" style="4"/>
+    <col min="1" max="5" width="3.6328125" style="4"/>
+    <col min="6" max="6" width="3.6328125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="3.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="72"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="71"/>
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="73" t="s">
+      <c r="R1" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="75"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="74"/>
       <c r="Y1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="77"/>
-      <c r="AC1" s="77"/>
-      <c r="AD1" s="77"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="67"/>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="69"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA1" s="75"/>
+      <c r="AB1" s="76"/>
+      <c r="AC1" s="76"/>
+      <c r="AD1" s="76"/>
+      <c r="AE1" s="77"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="67"/>
+      <c r="AH1" s="67"/>
+      <c r="AI1" s="68"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="81"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="80"/>
       <c r="P2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="82" t="s">
+      <c r="R2" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="84"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="82"/>
+      <c r="U2" s="82"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="82"/>
+      <c r="X2" s="83"/>
       <c r="Y2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="76"/>
-      <c r="AB2" s="77"/>
-      <c r="AC2" s="77"/>
-      <c r="AD2" s="77"/>
-      <c r="AE2" s="78"/>
-      <c r="AF2" s="67"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="69"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA2" s="75"/>
+      <c r="AB2" s="76"/>
+      <c r="AC2" s="76"/>
+      <c r="AD2" s="76"/>
+      <c r="AE2" s="77"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="67"/>
+      <c r="AH2" s="67"/>
+      <c r="AI2" s="68"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="86"/>
-      <c r="W3" s="86"/>
-      <c r="X3" s="87"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="86"/>
       <c r="Y3" s="12" t="s">
         <v>6</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="76"/>
-      <c r="AB3" s="77"/>
-      <c r="AC3" s="77"/>
-      <c r="AD3" s="77"/>
-      <c r="AE3" s="78"/>
-      <c r="AF3" s="67"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="69"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA3" s="75"/>
+      <c r="AB3" s="76"/>
+      <c r="AC3" s="76"/>
+      <c r="AD3" s="76"/>
+      <c r="AE3" s="77"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="67"/>
+      <c r="AH3" s="67"/>
+      <c r="AI3" s="68"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>14</v>
       </c>
@@ -1981,8 +1990,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="24" t="str">
         <f>$B$5&amp;"3."</f>
         <v>6.3.</v>
@@ -1991,8 +2000,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="24" t="str">
         <f>$C$7&amp;"1."</f>
         <v>6.3.1.</v>
@@ -2001,35 +2010,35 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="24"/>
       <c r="E10" s="27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="30"/>
       <c r="E11" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="30"/>
       <c r="E12" s="27"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="24"/>
       <c r="E13" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="24"/>
       <c r="E14" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D15" s="51"/>
       <c r="E15" s="27" t="s">
         <v>17</v>
@@ -2041,7 +2050,7 @@
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="51"/>
       <c r="E16" s="27" t="s">
         <v>18</v>
@@ -2053,7 +2062,7 @@
       <c r="J16" s="27"/>
       <c r="K16" s="27"/>
     </row>
-    <row r="17" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="51"/>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
@@ -2063,7 +2072,7 @@
       <c r="J17" s="27"/>
       <c r="K17" s="27"/>
     </row>
-    <row r="18" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
       <c r="E18" s="27" t="s">
@@ -2075,7 +2084,7 @@
       <c r="J18" s="27"/>
       <c r="K18" s="27"/>
     </row>
-    <row r="19" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27" t="s">
@@ -2087,7 +2096,7 @@
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
     </row>
-    <row r="20" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="27"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27" t="s">
@@ -2099,7 +2108,7 @@
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
     </row>
-    <row r="21" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27"/>
@@ -2110,7 +2119,7 @@
       <c r="J21" s="27"/>
       <c r="K21" s="27"/>
     </row>
-    <row r="22" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D22" s="27"/>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
@@ -2120,7 +2129,7 @@
       <c r="J22" s="27"/>
       <c r="K22" s="27"/>
     </row>
-    <row r="23" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D23" s="51" t="str">
         <f>$C$7&amp;"2."</f>
         <v>6.3.2.</v>
@@ -2136,7 +2145,7 @@
       <c r="J23" s="27"/>
       <c r="K23" s="27"/>
     </row>
-    <row r="24" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="51"/>
       <c r="E24" s="51" t="str">
         <f>D23&amp;"1."</f>
@@ -2152,7 +2161,7 @@
       <c r="J24" s="27"/>
       <c r="K24" s="27"/>
     </row>
-    <row r="25" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27" t="s">
@@ -2164,10 +2173,10 @@
       <c r="J25" s="27"/>
       <c r="K25" s="27"/>
     </row>
-    <row r="26" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D27" s="29"/>
       <c r="F27" s="15" t="s">
         <v>12</v>
@@ -2203,7 +2212,7 @@
       <c r="AG27" s="16"/>
       <c r="AH27" s="17"/>
     </row>
-    <row r="28" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D28" s="29"/>
       <c r="F28" s="18" t="s">
         <v>23</v>
@@ -2239,7 +2248,7 @@
       <c r="AG28" s="19"/>
       <c r="AH28" s="20"/>
     </row>
-    <row r="29" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D29" s="29"/>
       <c r="F29" s="21"/>
       <c r="G29" s="22"/>
@@ -2273,7 +2282,7 @@
       <c r="AG29" s="22"/>
       <c r="AH29" s="23"/>
     </row>
-    <row r="30" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D30" s="29"/>
       <c r="F30" s="21"/>
       <c r="G30" s="22"/>
@@ -2307,7 +2316,7 @@
       <c r="AG30" s="22"/>
       <c r="AH30" s="23"/>
     </row>
-    <row r="31" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D31" s="29"/>
       <c r="F31" s="21"/>
       <c r="G31" s="22"/>
@@ -2339,7 +2348,7 @@
       <c r="AG31" s="22"/>
       <c r="AH31" s="23"/>
     </row>
-    <row r="32" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D32" s="29"/>
       <c r="F32" s="36" t="s">
         <v>24</v>
@@ -2375,7 +2384,7 @@
       <c r="AG32" s="37"/>
       <c r="AH32" s="38"/>
     </row>
-    <row r="33" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D33" s="29"/>
       <c r="F33" s="34"/>
       <c r="G33" s="35"/>
@@ -2407,7 +2416,7 @@
       <c r="AG33" s="35"/>
       <c r="AH33" s="39"/>
     </row>
-    <row r="34" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F34" s="32"/>
       <c r="G34" s="32"/>
       <c r="H34" s="32"/>
@@ -2438,14 +2447,14 @@
       <c r="AG34" s="32"/>
       <c r="AH34" s="32"/>
     </row>
-    <row r="35" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="29"/>
       <c r="D35" s="29"/>
       <c r="F35" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="29"/>
       <c r="D36" s="29"/>
       <c r="F36" s="15" t="str">
@@ -2485,7 +2494,7 @@
       <c r="AG36" s="16"/>
       <c r="AH36" s="17"/>
     </row>
-    <row r="37" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="29"/>
       <c r="D37" s="29"/>
       <c r="F37" s="21" t="str">
@@ -2525,7 +2534,7 @@
       <c r="AG37" s="49"/>
       <c r="AH37" s="50"/>
     </row>
-    <row r="38" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
       <c r="D38" s="29"/>
       <c r="F38" s="44" t="str">
@@ -2565,7 +2574,7 @@
       <c r="AG38" s="60"/>
       <c r="AH38" s="61"/>
     </row>
-    <row r="39" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
       <c r="H39" s="32"/>
@@ -2596,7 +2605,7 @@
       <c r="AG39" s="32"/>
       <c r="AH39" s="32"/>
     </row>
-    <row r="40" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F40" s="29" t="s">
         <v>94</v>
       </c>
@@ -2629,7 +2638,7 @@
       <c r="AG40" s="32"/>
       <c r="AH40" s="32"/>
     </row>
-    <row r="41" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G41" s="32"/>
       <c r="H41" s="32"/>
       <c r="I41" s="32"/>
@@ -2659,7 +2668,7 @@
       <c r="AG41" s="32"/>
       <c r="AH41" s="32"/>
     </row>
-    <row r="42" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F42" s="32" t="s">
         <v>95</v>
       </c>
@@ -2692,7 +2701,7 @@
       <c r="AG42" s="32"/>
       <c r="AH42" s="32"/>
     </row>
-    <row r="43" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F43" s="32" t="s">
         <v>96</v>
       </c>
@@ -2725,7 +2734,7 @@
       <c r="AG43" s="32"/>
       <c r="AH43" s="32"/>
     </row>
-    <row r="44" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F44" s="32" t="s">
         <v>97</v>
       </c>
@@ -2758,7 +2767,7 @@
       <c r="AG44" s="32"/>
       <c r="AH44" s="32"/>
     </row>
-    <row r="45" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F45" s="32" t="s">
         <v>98</v>
       </c>
@@ -2822,7 +2831,7 @@
       <c r="AG46" s="32"/>
       <c r="AH46" s="32"/>
     </row>
-    <row r="47" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E47" s="30" t="str">
         <f>D23&amp;"2."</f>
         <v>6.3.2.2.</v>
@@ -2859,10 +2868,10 @@
       <c r="AG47" s="32"/>
       <c r="AH47" s="32"/>
     </row>
-    <row r="48" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E48" s="30"/>
       <c r="F48" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G48" s="32"/>
       <c r="H48" s="32"/>
@@ -2893,9 +2902,9 @@
       <c r="AG48" s="32"/>
       <c r="AH48" s="32"/>
     </row>
-    <row r="49" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F49" s="32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G49" s="32"/>
       <c r="H49" s="32"/>
@@ -2926,7 +2935,7 @@
       <c r="AG49" s="32"/>
       <c r="AH49" s="32"/>
     </row>
-    <row r="50" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
       <c r="H50" s="32"/>
@@ -2957,9 +2966,9 @@
       <c r="AG50" s="32"/>
       <c r="AH50" s="32"/>
     </row>
-    <row r="51" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F51" s="66" t="s">
-        <v>100</v>
+    <row r="51" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F51" s="88" t="s">
+        <v>111</v>
       </c>
       <c r="G51" s="32"/>
       <c r="H51" s="32"/>
@@ -2990,9 +2999,9 @@
       <c r="AG51" s="32"/>
       <c r="AH51" s="32"/>
     </row>
-    <row r="52" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D54" s="48" t="str">
         <f>$C$7&amp;"3."</f>
         <v>6.3.3.</v>
@@ -3001,7 +3010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E55" s="48" t="str">
         <f>D54&amp;"1."</f>
         <v>6.3.3.1.</v>
@@ -3011,61 +3020,61 @@
         <v>メールテンプレート手段</v>
       </c>
     </row>
-    <row r="56" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E56" s="48"/>
       <c r="F56" s="47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E57" s="48"/>
       <c r="F57" s="47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E58" s="48"/>
     </row>
-    <row r="59" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E59" s="48"/>
       <c r="F59" s="47" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="60" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E60" s="48"/>
       <c r="F60" s="47" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E61" s="48"/>
     </row>
-    <row r="62" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E62" s="48"/>
       <c r="F62" s="47" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E63" s="48"/>
       <c r="F63" s="47" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="64" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E64" s="48"/>
     </row>
-    <row r="65" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E65" s="48"/>
       <c r="F65" s="47" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="66" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E66" s="48"/>
     </row>
-    <row r="67" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E67" s="48"/>
       <c r="F67" s="47" t="s">
         <v>80</v>
@@ -3074,7 +3083,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E68" s="48"/>
       <c r="F68" s="47" t="s">
         <v>84</v>
@@ -3083,7 +3092,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E69" s="48"/>
       <c r="F69" s="47" t="s">
         <v>85</v>
@@ -3092,23 +3101,23 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E70" s="48"/>
     </row>
-    <row r="71" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E71" s="48"/>
       <c r="F71" s="47" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E72" s="48"/>
       <c r="F72" s="47" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D74" s="48" t="str">
         <f>$C$7&amp;"4."</f>
         <v>6.3.4.</v>
@@ -3117,7 +3126,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E75" s="24" t="str">
         <f>D74&amp;"1."</f>
         <v>6.3.4.1.</v>
@@ -3127,7 +3136,7 @@
         <v>メールフォーマット手段</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F76" s="15" t="s">
         <v>53</v>
       </c>
@@ -3164,7 +3173,7 @@
       <c r="AG76" s="16"/>
       <c r="AH76" s="17"/>
     </row>
-    <row r="77" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F77" s="44" t="s">
         <v>56</v>
       </c>
@@ -3201,11 +3210,11 @@
       <c r="AG77" s="60"/>
       <c r="AH77" s="61"/>
     </row>
-    <row r="78" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E79" s="24"/>
     </row>
-    <row r="80" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="28"/>
       <c r="B80" s="28"/>
       <c r="C80" s="28"/>
@@ -3247,7 +3256,7 @@
       <c r="AH80" s="28"/>
       <c r="AI80" s="28"/>
     </row>
-    <row r="81" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="28"/>
       <c r="B81" s="28"/>
       <c r="C81" s="28"/>
@@ -3290,7 +3299,7 @@
       <c r="AH81" s="28"/>
       <c r="AI81" s="28"/>
     </row>
-    <row r="82" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="28"/>
       <c r="B82" s="28"/>
       <c r="C82" s="28"/>
@@ -3329,7 +3338,7 @@
       <c r="AH82" s="28"/>
       <c r="AI82" s="28"/>
     </row>
-    <row r="83" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="28"/>
       <c r="B83" s="28"/>
       <c r="C83" s="28"/>
@@ -3366,7 +3375,7 @@
       <c r="AH83" s="28"/>
       <c r="AI83" s="28"/>
     </row>
-    <row r="84" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="28"/>
       <c r="B84" s="28"/>
       <c r="C84" s="28"/>
@@ -3409,7 +3418,7 @@
       <c r="AH84" s="28"/>
       <c r="AI84" s="28"/>
     </row>
-    <row r="85" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="28"/>
       <c r="B85" s="28"/>
       <c r="C85" s="28"/>
@@ -3448,7 +3457,7 @@
       <c r="AH85" s="28"/>
       <c r="AI85" s="28"/>
     </row>
-    <row r="86" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="43"/>
       <c r="B86" s="43"/>
       <c r="C86" s="43"/>
@@ -3485,7 +3494,7 @@
       <c r="AH86" s="28"/>
       <c r="AI86" s="28"/>
     </row>
-    <row r="87" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="43"/>
       <c r="B87" s="27"/>
       <c r="C87" s="43"/>
@@ -3529,7 +3538,7 @@
       <c r="AG87" s="41"/>
       <c r="AH87" s="42"/>
     </row>
-    <row r="88" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="27"/>
       <c r="B88" s="27"/>
       <c r="C88" s="43"/>
@@ -3573,7 +3582,7 @@
       <c r="AG88" s="37"/>
       <c r="AH88" s="38"/>
     </row>
-    <row r="89" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="27"/>
       <c r="B89" s="27"/>
       <c r="C89" s="43"/>
@@ -3617,7 +3626,7 @@
       <c r="AG89" s="37"/>
       <c r="AH89" s="38"/>
     </row>
-    <row r="90" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="27"/>
       <c r="B90" s="27"/>
       <c r="C90" s="43"/>
@@ -3655,7 +3664,7 @@
       <c r="AG90" s="32"/>
       <c r="AH90" s="33"/>
     </row>
-    <row r="91" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="27"/>
       <c r="B91" s="27"/>
       <c r="C91" s="43"/>
@@ -3695,7 +3704,7 @@
       <c r="AG91" s="35"/>
       <c r="AH91" s="39"/>
     </row>
-    <row r="92" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="27"/>
       <c r="B92" s="27"/>
       <c r="C92" s="43"/>
@@ -3731,7 +3740,7 @@
       <c r="AG92" s="32"/>
       <c r="AH92" s="32"/>
     </row>
-    <row r="93" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="28"/>
       <c r="B93" s="28"/>
       <c r="C93" s="28"/>
@@ -3770,7 +3779,7 @@
       <c r="AH93" s="28"/>
       <c r="AI93" s="28"/>
     </row>
-    <row r="94" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="43"/>
       <c r="B94" s="43"/>
       <c r="C94" s="43"/>
@@ -3807,7 +3816,7 @@
       <c r="AH94" s="28"/>
       <c r="AI94" s="28"/>
     </row>
-    <row r="95" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="43"/>
       <c r="B95" s="27"/>
       <c r="C95" s="43"/>
@@ -3851,7 +3860,7 @@
       <c r="AG95" s="41"/>
       <c r="AH95" s="42"/>
     </row>
-    <row r="96" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="27"/>
       <c r="B96" s="27"/>
       <c r="C96" s="43"/>
@@ -3895,7 +3904,7 @@
       <c r="AG96" s="37"/>
       <c r="AH96" s="38"/>
     </row>
-    <row r="97" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="27"/>
       <c r="B97" s="27"/>
       <c r="C97" s="43"/>
@@ -3939,7 +3948,7 @@
       <c r="AG97" s="45"/>
       <c r="AH97" s="46"/>
     </row>
-    <row r="98" spans="1:34" s="27" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:34" s="27" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C98" s="43"/>
       <c r="D98" s="43"/>
       <c r="E98" s="43"/>
@@ -3973,10 +3982,10 @@
       <c r="AG98" s="49"/>
       <c r="AH98" s="49"/>
     </row>
-    <row r="99" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C99" s="27"/>
     </row>
-    <row r="100" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C100" s="27"/>
       <c r="D100" s="25" t="str">
         <f>$C$7&amp;"6."</f>
@@ -3986,22 +3995,22 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C101" s="27"/>
       <c r="D101" s="25"/>
       <c r="E101" s="29" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C102" s="27"/>
       <c r="D102" s="25"/>
     </row>
-    <row r="103" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C103" s="27"/>
       <c r="D103" s="25"/>
     </row>
-    <row r="104" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="27"/>
       <c r="C104" s="27"/>
       <c r="D104" s="53" t="str">
@@ -4013,7 +4022,7 @@
       </c>
       <c r="F104" s="27"/>
     </row>
-    <row r="105" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="27"/>
       <c r="C105" s="27"/>
       <c r="D105" s="27"/>
@@ -4022,17 +4031,17 @@
       </c>
       <c r="F105" s="27"/>
     </row>
-    <row r="106" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="27"/>
       <c r="C106" s="27"/>
       <c r="D106" s="27"/>
       <c r="E106" s="27"/>
       <c r="F106" s="27"/>
     </row>
-    <row r="107" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C107" s="27"/>
     </row>
-    <row r="108" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="27"/>
       <c r="B108" s="27"/>
       <c r="C108" s="27"/>
@@ -4044,7 +4053,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="109" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="27"/>
       <c r="B109" s="27"/>
       <c r="C109" s="27"/>
@@ -4053,7 +4062,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="27"/>
       <c r="B110" s="27"/>
       <c r="C110" s="27"/>
@@ -4062,7 +4071,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="111" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="27"/>
       <c r="B111" s="27"/>
       <c r="C111" s="27"/>
@@ -4071,13 +4080,13 @@
         <v>73</v>
       </c>
     </row>
-    <row r="112" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="27"/>
       <c r="B112" s="27"/>
       <c r="C112" s="27"/>
       <c r="D112" s="25"/>
     </row>
-    <row r="113" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="27"/>
       <c r="B113" s="27"/>
       <c r="C113" s="27"/>
@@ -4102,10 +4111,10 @@
       <c r="U113" s="29"/>
       <c r="V113" s="29"/>
     </row>
-    <row r="114" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C114" s="27"/>
     </row>
-    <row r="115" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C115" s="27"/>
       <c r="E115" s="40" t="s">
         <v>79</v>
@@ -4132,7 +4141,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
     </row>
-    <row r="116" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C116" s="27"/>
       <c r="E116" s="44">
         <v>1</v>
@@ -4156,7 +4165,7 @@
       <c r="R116" s="45"/>
       <c r="S116" s="46"/>
     </row>
-    <row r="117" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C117" s="27"/>
       <c r="E117" s="34">
         <v>2</v>
@@ -4180,401 +4189,401 @@
       <c r="R117" s="45"/>
       <c r="S117" s="46"/>
     </row>
-    <row r="118" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C118" s="27"/>
     </row>
-    <row r="119" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F119" s="29"/>
     </row>
-    <row r="120" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="AF3:AI3"/>

--- a/nablarch_sample/アプリケーション方式設計書_6出力処理方式_6.3メール送信.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_6出力処理方式_6.3メール送信.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B720D016-DA04-49C4-B6A2-91106C764AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF808AF-2748-495A-9460-8E2F8ECBF0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.3.メール送信" sheetId="3" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6.3.メール送信'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'6.3.メール送信'!$A$1:$AI$119</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'6.3.メール送信'!$A$1:$AI$99</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'6.3.メール送信'!$A$1:$AI$99</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1436,6 +1430,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1501,9 +1498,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1843,146 +1837,146 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI508"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="5" width="3.6328125" style="4"/>
-    <col min="6" max="6" width="3.6328125" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="3.6328125" style="4"/>
+    <col min="1" max="5" width="3.625" style="4"/>
+    <col min="6" max="6" width="3.625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="3.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="71"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="72"/>
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="72" t="s">
+      <c r="R1" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="75"/>
       <c r="Y1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="75"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
-      <c r="AE1" s="77"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="67"/>
-      <c r="AH1" s="67"/>
-      <c r="AI1" s="68"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA1" s="76"/>
+      <c r="AB1" s="77"/>
+      <c r="AC1" s="77"/>
+      <c r="AD1" s="77"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="67"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="69"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="80"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="81"/>
       <c r="P2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="81" t="s">
+      <c r="R2" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="82"/>
-      <c r="T2" s="82"/>
-      <c r="U2" s="82"/>
-      <c r="V2" s="82"/>
-      <c r="W2" s="82"/>
-      <c r="X2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
+      <c r="W2" s="83"/>
+      <c r="X2" s="84"/>
       <c r="Y2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="75"/>
-      <c r="AB2" s="76"/>
-      <c r="AC2" s="76"/>
-      <c r="AD2" s="76"/>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="67"/>
-      <c r="AH2" s="67"/>
-      <c r="AI2" s="68"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA2" s="76"/>
+      <c r="AB2" s="77"/>
+      <c r="AC2" s="77"/>
+      <c r="AD2" s="77"/>
+      <c r="AE2" s="78"/>
+      <c r="AF2" s="67"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="69"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="85"/>
-      <c r="W3" s="85"/>
-      <c r="X3" s="86"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="86"/>
+      <c r="T3" s="86"/>
+      <c r="U3" s="86"/>
+      <c r="V3" s="86"/>
+      <c r="W3" s="86"/>
+      <c r="X3" s="87"/>
       <c r="Y3" s="12" t="s">
         <v>6</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="75"/>
-      <c r="AB3" s="76"/>
-      <c r="AC3" s="76"/>
-      <c r="AD3" s="76"/>
-      <c r="AE3" s="77"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="67"/>
-      <c r="AH3" s="67"/>
-      <c r="AI3" s="68"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA3" s="76"/>
+      <c r="AB3" s="77"/>
+      <c r="AC3" s="77"/>
+      <c r="AD3" s="77"/>
+      <c r="AE3" s="78"/>
+      <c r="AF3" s="67"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="69"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="24" t="s">
         <v>14</v>
       </c>
@@ -1990,8 +1984,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="24" t="str">
         <f>$B$5&amp;"3."</f>
         <v>6.3.</v>
@@ -2000,8 +1994,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D9" s="24" t="str">
         <f>$C$7&amp;"1."</f>
         <v>6.3.1.</v>
@@ -2010,35 +2004,35 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D10" s="24"/>
       <c r="E10" s="27" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D11" s="30"/>
       <c r="E11" s="27" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D12" s="30"/>
       <c r="E12" s="27"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D13" s="24"/>
       <c r="E13" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D14" s="24"/>
       <c r="E14" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D15" s="51"/>
       <c r="E15" s="27" t="s">
         <v>17</v>
@@ -2050,7 +2044,7 @@
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D16" s="51"/>
       <c r="E16" s="27" t="s">
         <v>18</v>
@@ -2062,7 +2056,7 @@
       <c r="J16" s="27"/>
       <c r="K16" s="27"/>
     </row>
-    <row r="17" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D17" s="51"/>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
@@ -2072,7 +2066,7 @@
       <c r="J17" s="27"/>
       <c r="K17" s="27"/>
     </row>
-    <row r="18" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
       <c r="E18" s="27" t="s">
@@ -2084,7 +2078,7 @@
       <c r="J18" s="27"/>
       <c r="K18" s="27"/>
     </row>
-    <row r="19" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27" t="s">
@@ -2096,7 +2090,7 @@
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
     </row>
-    <row r="20" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="27"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27" t="s">
@@ -2108,7 +2102,7 @@
       <c r="J20" s="27"/>
       <c r="K20" s="27"/>
     </row>
-    <row r="21" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27"/>
@@ -2119,7 +2113,7 @@
       <c r="J21" s="27"/>
       <c r="K21" s="27"/>
     </row>
-    <row r="22" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D22" s="27"/>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
@@ -2129,7 +2123,7 @@
       <c r="J22" s="27"/>
       <c r="K22" s="27"/>
     </row>
-    <row r="23" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D23" s="51" t="str">
         <f>$C$7&amp;"2."</f>
         <v>6.3.2.</v>
@@ -2145,7 +2139,7 @@
       <c r="J23" s="27"/>
       <c r="K23" s="27"/>
     </row>
-    <row r="24" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D24" s="51"/>
       <c r="E24" s="51" t="str">
         <f>D23&amp;"1."</f>
@@ -2161,7 +2155,7 @@
       <c r="J24" s="27"/>
       <c r="K24" s="27"/>
     </row>
-    <row r="25" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27" t="s">
@@ -2173,10 +2167,10 @@
       <c r="J25" s="27"/>
       <c r="K25" s="27"/>
     </row>
-    <row r="26" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E26" s="30"/>
     </row>
-    <row r="27" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D27" s="29"/>
       <c r="F27" s="15" t="s">
         <v>12</v>
@@ -2212,7 +2206,7 @@
       <c r="AG27" s="16"/>
       <c r="AH27" s="17"/>
     </row>
-    <row r="28" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D28" s="29"/>
       <c r="F28" s="18" t="s">
         <v>23</v>
@@ -2248,7 +2242,7 @@
       <c r="AG28" s="19"/>
       <c r="AH28" s="20"/>
     </row>
-    <row r="29" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D29" s="29"/>
       <c r="F29" s="21"/>
       <c r="G29" s="22"/>
@@ -2282,7 +2276,7 @@
       <c r="AG29" s="22"/>
       <c r="AH29" s="23"/>
     </row>
-    <row r="30" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D30" s="29"/>
       <c r="F30" s="21"/>
       <c r="G30" s="22"/>
@@ -2316,7 +2310,7 @@
       <c r="AG30" s="22"/>
       <c r="AH30" s="23"/>
     </row>
-    <row r="31" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D31" s="29"/>
       <c r="F31" s="21"/>
       <c r="G31" s="22"/>
@@ -2348,7 +2342,7 @@
       <c r="AG31" s="22"/>
       <c r="AH31" s="23"/>
     </row>
-    <row r="32" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D32" s="29"/>
       <c r="F32" s="36" t="s">
         <v>24</v>
@@ -2384,7 +2378,7 @@
       <c r="AG32" s="37"/>
       <c r="AH32" s="38"/>
     </row>
-    <row r="33" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D33" s="29"/>
       <c r="F33" s="34"/>
       <c r="G33" s="35"/>
@@ -2416,7 +2410,7 @@
       <c r="AG33" s="35"/>
       <c r="AH33" s="39"/>
     </row>
-    <row r="34" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F34" s="32"/>
       <c r="G34" s="32"/>
       <c r="H34" s="32"/>
@@ -2447,14 +2441,14 @@
       <c r="AG34" s="32"/>
       <c r="AH34" s="32"/>
     </row>
-    <row r="35" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="29"/>
       <c r="D35" s="29"/>
       <c r="F35" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="29"/>
       <c r="D36" s="29"/>
       <c r="F36" s="15" t="str">
@@ -2494,7 +2488,7 @@
       <c r="AG36" s="16"/>
       <c r="AH36" s="17"/>
     </row>
-    <row r="37" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="29"/>
       <c r="D37" s="29"/>
       <c r="F37" s="21" t="str">
@@ -2534,7 +2528,7 @@
       <c r="AG37" s="49"/>
       <c r="AH37" s="50"/>
     </row>
-    <row r="38" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="29"/>
       <c r="D38" s="29"/>
       <c r="F38" s="44" t="str">
@@ -2574,7 +2568,7 @@
       <c r="AG38" s="60"/>
       <c r="AH38" s="61"/>
     </row>
-    <row r="39" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
       <c r="H39" s="32"/>
@@ -2605,7 +2599,7 @@
       <c r="AG39" s="32"/>
       <c r="AH39" s="32"/>
     </row>
-    <row r="40" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F40" s="29" t="s">
         <v>94</v>
       </c>
@@ -2638,7 +2632,7 @@
       <c r="AG40" s="32"/>
       <c r="AH40" s="32"/>
     </row>
-    <row r="41" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G41" s="32"/>
       <c r="H41" s="32"/>
       <c r="I41" s="32"/>
@@ -2668,7 +2662,7 @@
       <c r="AG41" s="32"/>
       <c r="AH41" s="32"/>
     </row>
-    <row r="42" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F42" s="32" t="s">
         <v>95</v>
       </c>
@@ -2701,7 +2695,7 @@
       <c r="AG42" s="32"/>
       <c r="AH42" s="32"/>
     </row>
-    <row r="43" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F43" s="32" t="s">
         <v>96</v>
       </c>
@@ -2734,7 +2728,7 @@
       <c r="AG43" s="32"/>
       <c r="AH43" s="32"/>
     </row>
-    <row r="44" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F44" s="32" t="s">
         <v>97</v>
       </c>
@@ -2767,7 +2761,7 @@
       <c r="AG44" s="32"/>
       <c r="AH44" s="32"/>
     </row>
-    <row r="45" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F45" s="32" t="s">
         <v>98</v>
       </c>
@@ -2800,7 +2794,7 @@
       <c r="AG45" s="32"/>
       <c r="AH45" s="32"/>
     </row>
-    <row r="46" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
       <c r="H46" s="32"/>
@@ -2831,7 +2825,7 @@
       <c r="AG46" s="32"/>
       <c r="AH46" s="32"/>
     </row>
-    <row r="47" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E47" s="30" t="str">
         <f>D23&amp;"2."</f>
         <v>6.3.2.2.</v>
@@ -2868,7 +2862,7 @@
       <c r="AG47" s="32"/>
       <c r="AH47" s="32"/>
     </row>
-    <row r="48" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E48" s="30"/>
       <c r="F48" s="32" t="s">
         <v>102</v>
@@ -2902,7 +2896,7 @@
       <c r="AG48" s="32"/>
       <c r="AH48" s="32"/>
     </row>
-    <row r="49" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F49" s="32" t="s">
         <v>103</v>
       </c>
@@ -2935,7 +2929,7 @@
       <c r="AG49" s="32"/>
       <c r="AH49" s="32"/>
     </row>
-    <row r="50" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
       <c r="H50" s="32"/>
@@ -2966,8 +2960,8 @@
       <c r="AG50" s="32"/>
       <c r="AH50" s="32"/>
     </row>
-    <row r="51" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F51" s="88" t="s">
+    <row r="51" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F51" s="66" t="s">
         <v>111</v>
       </c>
       <c r="G51" s="32"/>
@@ -2999,9 +2993,9 @@
       <c r="AG51" s="32"/>
       <c r="AH51" s="32"/>
     </row>
-    <row r="52" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D54" s="48" t="str">
         <f>$C$7&amp;"3."</f>
         <v>6.3.3.</v>
@@ -3010,7 +3004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E55" s="48" t="str">
         <f>D54&amp;"1."</f>
         <v>6.3.3.1.</v>
@@ -3020,61 +3014,61 @@
         <v>メールテンプレート手段</v>
       </c>
     </row>
-    <row r="56" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E56" s="48"/>
       <c r="F56" s="47" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E57" s="48"/>
       <c r="F57" s="47" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E58" s="48"/>
     </row>
-    <row r="59" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E59" s="48"/>
       <c r="F59" s="47" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E60" s="48"/>
       <c r="F60" s="47" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="61" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E61" s="48"/>
     </row>
-    <row r="62" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E62" s="48"/>
       <c r="F62" s="47" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E63" s="48"/>
       <c r="F63" s="47" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="64" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="4:34" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E64" s="48"/>
     </row>
-    <row r="65" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E65" s="48"/>
       <c r="F65" s="47" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="66" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E66" s="48"/>
     </row>
-    <row r="67" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E67" s="48"/>
       <c r="F67" s="47" t="s">
         <v>80</v>
@@ -3083,7 +3077,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E68" s="48"/>
       <c r="F68" s="47" t="s">
         <v>84</v>
@@ -3092,7 +3086,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E69" s="48"/>
       <c r="F69" s="47" t="s">
         <v>85</v>
@@ -3101,23 +3095,23 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E70" s="48"/>
     </row>
-    <row r="71" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E71" s="48"/>
       <c r="F71" s="47" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E72" s="48"/>
       <c r="F72" s="47" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" spans="1:35" s="47" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D74" s="48" t="str">
         <f>$C$7&amp;"4."</f>
         <v>6.3.4.</v>
@@ -3126,7 +3120,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E75" s="24" t="str">
         <f>D74&amp;"1."</f>
         <v>6.3.4.1.</v>
@@ -3136,7 +3130,7 @@
         <v>メールフォーマット手段</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F76" s="15" t="s">
         <v>53</v>
       </c>
@@ -3173,7 +3167,7 @@
       <c r="AG76" s="16"/>
       <c r="AH76" s="17"/>
     </row>
-    <row r="77" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="44" t="s">
         <v>56</v>
       </c>
@@ -3210,11 +3204,11 @@
       <c r="AG77" s="60"/>
       <c r="AH77" s="61"/>
     </row>
-    <row r="78" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E79" s="24"/>
     </row>
-    <row r="80" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="28"/>
       <c r="B80" s="28"/>
       <c r="C80" s="28"/>
@@ -3256,7 +3250,7 @@
       <c r="AH80" s="28"/>
       <c r="AI80" s="28"/>
     </row>
-    <row r="81" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="28"/>
       <c r="B81" s="28"/>
       <c r="C81" s="28"/>
@@ -3299,7 +3293,7 @@
       <c r="AH81" s="28"/>
       <c r="AI81" s="28"/>
     </row>
-    <row r="82" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="28"/>
       <c r="B82" s="28"/>
       <c r="C82" s="28"/>
@@ -3338,7 +3332,7 @@
       <c r="AH82" s="28"/>
       <c r="AI82" s="28"/>
     </row>
-    <row r="83" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="28"/>
       <c r="B83" s="28"/>
       <c r="C83" s="28"/>
@@ -3375,7 +3369,7 @@
       <c r="AH83" s="28"/>
       <c r="AI83" s="28"/>
     </row>
-    <row r="84" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="28"/>
       <c r="B84" s="28"/>
       <c r="C84" s="28"/>
@@ -3418,7 +3412,7 @@
       <c r="AH84" s="28"/>
       <c r="AI84" s="28"/>
     </row>
-    <row r="85" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="28"/>
       <c r="B85" s="28"/>
       <c r="C85" s="28"/>
@@ -3457,7 +3451,7 @@
       <c r="AH85" s="28"/>
       <c r="AI85" s="28"/>
     </row>
-    <row r="86" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="43"/>
       <c r="B86" s="43"/>
       <c r="C86" s="43"/>
@@ -3494,7 +3488,7 @@
       <c r="AH86" s="28"/>
       <c r="AI86" s="28"/>
     </row>
-    <row r="87" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="43"/>
       <c r="B87" s="27"/>
       <c r="C87" s="43"/>
@@ -3538,7 +3532,7 @@
       <c r="AG87" s="41"/>
       <c r="AH87" s="42"/>
     </row>
-    <row r="88" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="27"/>
       <c r="B88" s="27"/>
       <c r="C88" s="43"/>
@@ -3582,7 +3576,7 @@
       <c r="AG88" s="37"/>
       <c r="AH88" s="38"/>
     </row>
-    <row r="89" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="27"/>
       <c r="B89" s="27"/>
       <c r="C89" s="43"/>
@@ -3626,7 +3620,7 @@
       <c r="AG89" s="37"/>
       <c r="AH89" s="38"/>
     </row>
-    <row r="90" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="27"/>
       <c r="B90" s="27"/>
       <c r="C90" s="43"/>
@@ -3664,7 +3658,7 @@
       <c r="AG90" s="32"/>
       <c r="AH90" s="33"/>
     </row>
-    <row r="91" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="27"/>
       <c r="B91" s="27"/>
       <c r="C91" s="43"/>
@@ -3704,7 +3698,7 @@
       <c r="AG91" s="35"/>
       <c r="AH91" s="39"/>
     </row>
-    <row r="92" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="27"/>
       <c r="B92" s="27"/>
       <c r="C92" s="43"/>
@@ -3740,7 +3734,7 @@
       <c r="AG92" s="32"/>
       <c r="AH92" s="32"/>
     </row>
-    <row r="93" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="28"/>
       <c r="B93" s="28"/>
       <c r="C93" s="28"/>
@@ -3779,7 +3773,7 @@
       <c r="AH93" s="28"/>
       <c r="AI93" s="28"/>
     </row>
-    <row r="94" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="43"/>
       <c r="B94" s="43"/>
       <c r="C94" s="43"/>
@@ -3816,7 +3810,7 @@
       <c r="AH94" s="28"/>
       <c r="AI94" s="28"/>
     </row>
-    <row r="95" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="43"/>
       <c r="B95" s="27"/>
       <c r="C95" s="43"/>
@@ -3860,7 +3854,7 @@
       <c r="AG95" s="41"/>
       <c r="AH95" s="42"/>
     </row>
-    <row r="96" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:35" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="27"/>
       <c r="B96" s="27"/>
       <c r="C96" s="43"/>
@@ -3904,7 +3898,7 @@
       <c r="AG96" s="37"/>
       <c r="AH96" s="38"/>
     </row>
-    <row r="97" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="27"/>
       <c r="B97" s="27"/>
       <c r="C97" s="43"/>
@@ -3948,7 +3942,7 @@
       <c r="AG97" s="45"/>
       <c r="AH97" s="46"/>
     </row>
-    <row r="98" spans="1:34" s="27" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:34" s="27" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C98" s="43"/>
       <c r="D98" s="43"/>
       <c r="E98" s="43"/>
@@ -3982,10 +3976,10 @@
       <c r="AG98" s="49"/>
       <c r="AH98" s="49"/>
     </row>
-    <row r="99" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C99" s="27"/>
     </row>
-    <row r="100" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C100" s="27"/>
       <c r="D100" s="25" t="str">
         <f>$C$7&amp;"6."</f>
@@ -3995,22 +3989,22 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C101" s="27"/>
       <c r="D101" s="25"/>
       <c r="E101" s="29" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C102" s="27"/>
       <c r="D102" s="25"/>
     </row>
-    <row r="103" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C103" s="27"/>
       <c r="D103" s="25"/>
     </row>
-    <row r="104" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B104" s="27"/>
       <c r="C104" s="27"/>
       <c r="D104" s="53" t="str">
@@ -4022,7 +4016,7 @@
       </c>
       <c r="F104" s="27"/>
     </row>
-    <row r="105" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B105" s="27"/>
       <c r="C105" s="27"/>
       <c r="D105" s="27"/>
@@ -4031,17 +4025,17 @@
       </c>
       <c r="F105" s="27"/>
     </row>
-    <row r="106" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B106" s="27"/>
       <c r="C106" s="27"/>
       <c r="D106" s="27"/>
       <c r="E106" s="27"/>
       <c r="F106" s="27"/>
     </row>
-    <row r="107" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C107" s="27"/>
     </row>
-    <row r="108" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="27"/>
       <c r="B108" s="27"/>
       <c r="C108" s="27"/>
@@ -4053,7 +4047,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="109" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="27"/>
       <c r="B109" s="27"/>
       <c r="C109" s="27"/>
@@ -4062,7 +4056,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="27"/>
       <c r="B110" s="27"/>
       <c r="C110" s="27"/>
@@ -4071,7 +4065,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="111" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="27"/>
       <c r="B111" s="27"/>
       <c r="C111" s="27"/>
@@ -4080,13 +4074,13 @@
         <v>73</v>
       </c>
     </row>
-    <row r="112" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="27"/>
       <c r="B112" s="27"/>
       <c r="C112" s="27"/>
       <c r="D112" s="25"/>
     </row>
-    <row r="113" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="27"/>
       <c r="B113" s="27"/>
       <c r="C113" s="27"/>
@@ -4111,10 +4105,10 @@
       <c r="U113" s="29"/>
       <c r="V113" s="29"/>
     </row>
-    <row r="114" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="27"/>
     </row>
-    <row r="115" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:22" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="27"/>
       <c r="E115" s="40" t="s">
         <v>79</v>
@@ -4141,7 +4135,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
     </row>
-    <row r="116" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C116" s="27"/>
       <c r="E116" s="44">
         <v>1</v>
@@ -4165,7 +4159,7 @@
       <c r="R116" s="45"/>
       <c r="S116" s="46"/>
     </row>
-    <row r="117" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="27"/>
       <c r="E117" s="34">
         <v>2</v>
@@ -4189,401 +4183,401 @@
       <c r="R117" s="45"/>
       <c r="S117" s="46"/>
     </row>
-    <row r="118" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="27"/>
     </row>
-    <row r="119" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F119" s="29"/>
     </row>
-    <row r="120" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="AF3:AI3"/>
